--- a/chongli_care_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/chongli_care_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度养护" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度养护明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="年度养护" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="年度养护明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6304,7 +6304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6315,6 +6315,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6358,6 +6359,11 @@
           <t>时间</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6398,6 +6404,11 @@
           <t>10:28:34</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6428,6 +6439,11 @@
           <t>17:13:24</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6468,6 +6484,11 @@
           <t>19:12:39</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6498,6 +6519,11 @@
           <t>08:37:19</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6538,6 +6564,11 @@
           <t>16:45:12</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6578,6 +6609,11 @@
           <t>17:09:23</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6618,6 +6654,11 @@
           <t>23:34:59</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6658,6 +6699,11 @@
           <t>17:57:51</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6698,6 +6744,11 @@
           <t>22:14:41</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6728,6 +6779,11 @@
           <t>21:24:20</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>布乖（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6768,6 +6824,11 @@
           <t>13:55:18</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6798,6 +6859,11 @@
           <t>16:53:56</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>布乖（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6828,6 +6894,11 @@
           <t>10:43:58</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>布乖（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6868,6 +6939,11 @@
           <t>21:11:40</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>张凯</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6908,6 +6984,11 @@
           <t>19:45:43</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>布乖（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6948,6 +7029,11 @@
           <t>18:22:22</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6988,6 +7074,11 @@
           <t>19:07:03</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7028,6 +7119,11 @@
           <t>12:55:35</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7068,6 +7164,11 @@
           <t>17:07:24</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7108,6 +7209,11 @@
           <t>19:18:54</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7136,6 +7242,11 @@
       <c r="H22" t="inlineStr">
         <is>
           <t>13:36:32</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
         </is>
       </c>
     </row>
